--- a/kerntabellen/gemeente_energiehuis.xlsx
+++ b/kerntabellen/gemeente_energiehuis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\gebiedsniveaus\kerntabellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA4F1B8-B5CB-4E5A-9ACA-998711C39499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0F8424-E720-4A0E-AEAA-7151E3286B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E197355D-8CA8-41FC-91D5-9D8F4A552916}"/>
   </bookViews>
@@ -959,12 +959,6 @@
     <t>WoonEnergie Zennevallei</t>
   </si>
   <si>
-    <t>Name werkingsgebied energiehuis</t>
-  </si>
-  <si>
-    <t>werkingsgebied energiehuis</t>
-  </si>
-  <si>
     <t>gemeente</t>
   </si>
   <si>
@@ -1059,6 +1053,12 @@
   </si>
   <si>
     <t>energ01</t>
+  </si>
+  <si>
+    <t>energiehuis</t>
+  </si>
+  <si>
+    <t>Name energiehuis</t>
   </si>
 </sst>
 </file>
@@ -1442,16 +1442,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="D1" t="s">
-        <v>307</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1462,7 +1462,7 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s">
         <v>64</v>
@@ -1476,7 +1476,7 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D3" t="s">
         <v>64</v>
@@ -1490,7 +1490,7 @@
         <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D4" t="s">
         <v>161</v>
@@ -1504,7 +1504,7 @@
         <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
         <v>161</v>
@@ -1518,7 +1518,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D6" t="s">
         <v>161</v>
@@ -1532,7 +1532,7 @@
         <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D7" t="s">
         <v>105</v>
@@ -1546,7 +1546,7 @@
         <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D8" t="s">
         <v>105</v>
@@ -1560,7 +1560,7 @@
         <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D9" t="s">
         <v>105</v>
@@ -1574,7 +1574,7 @@
         <v>114</v>
       </c>
       <c r="C10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D10" t="s">
         <v>105</v>
@@ -1588,7 +1588,7 @@
         <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D11" t="s">
         <v>161</v>
@@ -1602,7 +1602,7 @@
         <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D12" t="s">
         <v>161</v>
@@ -1616,7 +1616,7 @@
         <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D13" t="s">
         <v>161</v>
@@ -1630,7 +1630,7 @@
         <v>279</v>
       </c>
       <c r="C14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
@@ -1644,7 +1644,7 @@
         <v>282</v>
       </c>
       <c r="C15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
@@ -1658,7 +1658,7 @@
         <v>284</v>
       </c>
       <c r="C16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D16" t="s">
         <v>46</v>
@@ -1672,7 +1672,7 @@
         <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D17" t="s">
         <v>46</v>
@@ -1686,7 +1686,7 @@
         <v>286</v>
       </c>
       <c r="C18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D18" t="s">
         <v>46</v>
@@ -1700,7 +1700,7 @@
         <v>163</v>
       </c>
       <c r="C19" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D19" t="s">
         <v>161</v>
@@ -1714,7 +1714,7 @@
         <v>189</v>
       </c>
       <c r="C20" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D20" t="s">
         <v>161</v>
@@ -1728,7 +1728,7 @@
         <v>176</v>
       </c>
       <c r="C21" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D21" t="s">
         <v>161</v>
@@ -1742,7 +1742,7 @@
         <v>179</v>
       </c>
       <c r="C22" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D22" t="s">
         <v>161</v>
@@ -1756,7 +1756,7 @@
         <v>188</v>
       </c>
       <c r="C23" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D23" t="s">
         <v>161</v>
@@ -1770,7 +1770,7 @@
         <v>274</v>
       </c>
       <c r="C24" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D24" t="s">
         <v>269</v>
@@ -1784,7 +1784,7 @@
         <v>268</v>
       </c>
       <c r="C25" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D25" t="s">
         <v>269</v>
@@ -1798,7 +1798,7 @@
         <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D26" t="s">
         <v>64</v>
@@ -1812,7 +1812,7 @@
         <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D27" t="s">
         <v>64</v>
@@ -1826,7 +1826,7 @@
         <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D28" t="s">
         <v>64</v>
@@ -1840,7 +1840,7 @@
         <v>280</v>
       </c>
       <c r="C29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D29" t="s">
         <v>46</v>
@@ -1854,7 +1854,7 @@
         <v>294</v>
       </c>
       <c r="C30" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D30" t="s">
         <v>46</v>
@@ -1868,7 +1868,7 @@
         <v>287</v>
       </c>
       <c r="C31" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D31" t="s">
         <v>46</v>
@@ -1882,7 +1882,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D32" t="s">
         <v>45</v>
@@ -1896,7 +1896,7 @@
         <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D33" t="s">
         <v>45</v>
@@ -1910,7 +1910,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D34" t="s">
         <v>45</v>
@@ -1924,7 +1924,7 @@
         <v>302</v>
       </c>
       <c r="C35" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D35" t="s">
         <v>46</v>
@@ -1938,7 +1938,7 @@
         <v>300</v>
       </c>
       <c r="C36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
@@ -1952,7 +1952,7 @@
         <v>301</v>
       </c>
       <c r="C37" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D37" t="s">
         <v>46</v>
@@ -1966,7 +1966,7 @@
         <v>304</v>
       </c>
       <c r="C38" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
@@ -1980,7 +1980,7 @@
         <v>303</v>
       </c>
       <c r="C39" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D39" t="s">
         <v>46</v>
@@ -1994,7 +1994,7 @@
         <v>275</v>
       </c>
       <c r="C40" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D40" t="s">
         <v>269</v>
@@ -2008,7 +2008,7 @@
         <v>270</v>
       </c>
       <c r="C41" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D41" t="s">
         <v>269</v>
@@ -2022,7 +2022,7 @@
         <v>272</v>
       </c>
       <c r="C42" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D42" t="s">
         <v>269</v>
@@ -2036,7 +2036,7 @@
         <v>271</v>
       </c>
       <c r="C43" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D43" t="s">
         <v>269</v>
@@ -2050,7 +2050,7 @@
         <v>273</v>
       </c>
       <c r="C44" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D44" t="s">
         <v>269</v>
@@ -2064,7 +2064,7 @@
         <v>65</v>
       </c>
       <c r="C45" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D45" t="s">
         <v>64</v>
@@ -2078,7 +2078,7 @@
         <v>71</v>
       </c>
       <c r="C46" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D46" t="s">
         <v>64</v>
@@ -2092,7 +2092,7 @@
         <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D47" t="s">
         <v>64</v>
@@ -2106,7 +2106,7 @@
         <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D48" t="s">
         <v>64</v>
@@ -2120,7 +2120,7 @@
         <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D49" t="s">
         <v>64</v>
@@ -2134,7 +2134,7 @@
         <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D50" t="s">
         <v>64</v>
@@ -2148,7 +2148,7 @@
         <v>66</v>
       </c>
       <c r="C51" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D51" t="s">
         <v>64</v>
@@ -2162,7 +2162,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D52" t="s">
         <v>64</v>
@@ -2176,7 +2176,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D53" t="s">
         <v>64</v>
@@ -2190,7 +2190,7 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
@@ -2204,7 +2204,7 @@
         <v>98</v>
       </c>
       <c r="C55" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D55" t="s">
         <v>64</v>
@@ -2218,7 +2218,7 @@
         <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D56" t="s">
         <v>64</v>
@@ -2232,7 +2232,7 @@
         <v>99</v>
       </c>
       <c r="C57" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D57" t="s">
         <v>64</v>
@@ -2246,7 +2246,7 @@
         <v>252</v>
       </c>
       <c r="C58" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D58" t="s">
         <v>245</v>
@@ -2260,7 +2260,7 @@
         <v>254</v>
       </c>
       <c r="C59" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D59" t="s">
         <v>245</v>
@@ -2274,7 +2274,7 @@
         <v>261</v>
       </c>
       <c r="C60" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D60" t="s">
         <v>245</v>
@@ -2288,7 +2288,7 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D61" t="s">
         <v>245</v>
@@ -2302,7 +2302,7 @@
         <v>43</v>
       </c>
       <c r="C62" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D62" t="s">
         <v>305</v>
@@ -2316,7 +2316,7 @@
         <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D63" t="s">
         <v>191</v>
@@ -2330,7 +2330,7 @@
         <v>194</v>
       </c>
       <c r="C64" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D64" t="s">
         <v>191</v>
@@ -2344,7 +2344,7 @@
         <v>202</v>
       </c>
       <c r="C65" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D65" t="s">
         <v>191</v>
@@ -2358,7 +2358,7 @@
         <v>205</v>
       </c>
       <c r="C66" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D66" t="s">
         <v>191</v>
@@ -2372,7 +2372,7 @@
         <v>208</v>
       </c>
       <c r="C67" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D67" t="s">
         <v>191</v>
@@ -2386,7 +2386,7 @@
         <v>210</v>
       </c>
       <c r="C68" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D68" t="s">
         <v>191</v>
@@ -2400,7 +2400,7 @@
         <v>197</v>
       </c>
       <c r="C69" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D69" t="s">
         <v>191</v>
@@ -2414,7 +2414,7 @@
         <v>190</v>
       </c>
       <c r="C70" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D70" t="s">
         <v>191</v>
@@ -2428,7 +2428,7 @@
         <v>201</v>
       </c>
       <c r="C71" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D71" t="s">
         <v>191</v>
@@ -2442,7 +2442,7 @@
         <v>203</v>
       </c>
       <c r="C72" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D72" t="s">
         <v>191</v>
@@ -2456,7 +2456,7 @@
         <v>213</v>
       </c>
       <c r="C73" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D73" t="s">
         <v>191</v>
@@ -2470,7 +2470,7 @@
         <v>204</v>
       </c>
       <c r="C74" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D74" t="s">
         <v>191</v>
@@ -2484,7 +2484,7 @@
         <v>212</v>
       </c>
       <c r="C75" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D75" t="s">
         <v>191</v>
@@ -2498,7 +2498,7 @@
         <v>195</v>
       </c>
       <c r="C76" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D76" t="s">
         <v>191</v>
@@ -2512,7 +2512,7 @@
         <v>196</v>
       </c>
       <c r="C77" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D77" t="s">
         <v>191</v>
@@ -2526,7 +2526,7 @@
         <v>206</v>
       </c>
       <c r="C78" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D78" t="s">
         <v>191</v>
@@ -2540,7 +2540,7 @@
         <v>209</v>
       </c>
       <c r="C79" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D79" t="s">
         <v>191</v>
@@ -2554,7 +2554,7 @@
         <v>198</v>
       </c>
       <c r="C80" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D80" t="s">
         <v>191</v>
@@ -2568,7 +2568,7 @@
         <v>199</v>
       </c>
       <c r="C81" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D81" t="s">
         <v>191</v>
@@ -2582,7 +2582,7 @@
         <v>200</v>
       </c>
       <c r="C82" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D82" t="s">
         <v>191</v>
@@ -2596,7 +2596,7 @@
         <v>192</v>
       </c>
       <c r="C83" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D83" t="s">
         <v>191</v>
@@ -2610,7 +2610,7 @@
         <v>207</v>
       </c>
       <c r="C84" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D84" t="s">
         <v>191</v>
@@ -2624,7 +2624,7 @@
         <v>211</v>
       </c>
       <c r="C85" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D85" t="s">
         <v>191</v>
@@ -2638,7 +2638,7 @@
         <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D86" t="s">
         <v>64</v>
@@ -2652,7 +2652,7 @@
         <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D87" t="s">
         <v>64</v>
@@ -2666,7 +2666,7 @@
         <v>85</v>
       </c>
       <c r="C88" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D88" t="s">
         <v>64</v>
@@ -2680,7 +2680,7 @@
         <v>113</v>
       </c>
       <c r="C89" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D89" t="s">
         <v>105</v>
@@ -2694,7 +2694,7 @@
         <v>52</v>
       </c>
       <c r="C90" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D90" t="s">
         <v>45</v>
@@ -2708,7 +2708,7 @@
         <v>104</v>
       </c>
       <c r="C91" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D91" t="s">
         <v>105</v>
@@ -2722,7 +2722,7 @@
         <v>63</v>
       </c>
       <c r="C92" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D92" t="s">
         <v>64</v>
@@ -2736,7 +2736,7 @@
         <v>67</v>
       </c>
       <c r="C93" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D93" t="s">
         <v>64</v>
@@ -2750,7 +2750,7 @@
         <v>90</v>
       </c>
       <c r="C94" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D94" t="s">
         <v>64</v>
@@ -2764,7 +2764,7 @@
         <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D95" t="s">
         <v>64</v>
@@ -2778,7 +2778,7 @@
         <v>128</v>
       </c>
       <c r="C96" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D96" t="s">
         <v>122</v>
@@ -2792,7 +2792,7 @@
         <v>131</v>
       </c>
       <c r="C97" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D97" t="s">
         <v>122</v>
@@ -2806,7 +2806,7 @@
         <v>132</v>
       </c>
       <c r="C98" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D98" t="s">
         <v>122</v>
@@ -2820,7 +2820,7 @@
         <v>142</v>
       </c>
       <c r="C99" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D99" t="s">
         <v>122</v>
@@ -2834,7 +2834,7 @@
         <v>145</v>
       </c>
       <c r="C100" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D100" t="s">
         <v>122</v>
@@ -2848,7 +2848,7 @@
         <v>137</v>
       </c>
       <c r="C101" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D101" t="s">
         <v>122</v>
@@ -2862,7 +2862,7 @@
         <v>143</v>
       </c>
       <c r="C102" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D102" t="s">
         <v>122</v>
@@ -2876,7 +2876,7 @@
         <v>144</v>
       </c>
       <c r="C103" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D103" t="s">
         <v>122</v>
@@ -2890,7 +2890,7 @@
         <v>146</v>
       </c>
       <c r="C104" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D104" t="s">
         <v>122</v>
@@ -2904,7 +2904,7 @@
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D105" t="s">
         <v>122</v>
@@ -2918,7 +2918,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D106" t="s">
         <v>122</v>
@@ -2932,7 +2932,7 @@
         <v>136</v>
       </c>
       <c r="C107" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D107" t="s">
         <v>122</v>
@@ -2946,7 +2946,7 @@
         <v>138</v>
       </c>
       <c r="C108" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D108" t="s">
         <v>122</v>
@@ -2960,7 +2960,7 @@
         <v>139</v>
       </c>
       <c r="C109" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D109" t="s">
         <v>122</v>
@@ -2974,7 +2974,7 @@
         <v>125</v>
       </c>
       <c r="C110" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D110" t="s">
         <v>122</v>
@@ -2988,7 +2988,7 @@
         <v>126</v>
       </c>
       <c r="C111" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D111" t="s">
         <v>122</v>
@@ -3002,7 +3002,7 @@
         <v>148</v>
       </c>
       <c r="C112" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D112" t="s">
         <v>122</v>
@@ -3016,7 +3016,7 @@
         <v>140</v>
       </c>
       <c r="C113" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D113" t="s">
         <v>122</v>
@@ -3030,7 +3030,7 @@
         <v>141</v>
       </c>
       <c r="C114" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D114" t="s">
         <v>122</v>
@@ -3044,7 +3044,7 @@
         <v>147</v>
       </c>
       <c r="C115" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D115" t="s">
         <v>122</v>
@@ -3058,7 +3058,7 @@
         <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D116" t="s">
         <v>122</v>
@@ -3072,7 +3072,7 @@
         <v>123</v>
       </c>
       <c r="C117" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D117" t="s">
         <v>122</v>
@@ -3086,7 +3086,7 @@
         <v>127</v>
       </c>
       <c r="C118" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D118" t="s">
         <v>122</v>
@@ -3100,7 +3100,7 @@
         <v>130</v>
       </c>
       <c r="C119" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D119" t="s">
         <v>122</v>
@@ -3114,7 +3114,7 @@
         <v>133</v>
       </c>
       <c r="C120" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D120" t="s">
         <v>122</v>
@@ -3128,7 +3128,7 @@
         <v>134</v>
       </c>
       <c r="C121" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D121" t="s">
         <v>122</v>
@@ -3142,7 +3142,7 @@
         <v>135</v>
       </c>
       <c r="C122" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D122" t="s">
         <v>122</v>
@@ -3156,7 +3156,7 @@
         <v>27</v>
       </c>
       <c r="C123" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D123" t="s">
         <v>1</v>
@@ -3170,7 +3170,7 @@
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D124" t="s">
         <v>1</v>
@@ -3184,7 +3184,7 @@
         <v>19</v>
       </c>
       <c r="C125" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D125" t="s">
         <v>1</v>
@@ -3198,7 +3198,7 @@
         <v>15</v>
       </c>
       <c r="C126" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D126" t="s">
         <v>1</v>
@@ -3212,7 +3212,7 @@
         <v>236</v>
       </c>
       <c r="C127" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D127" t="s">
         <v>224</v>
@@ -3226,7 +3226,7 @@
         <v>231</v>
       </c>
       <c r="C128" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D128" t="s">
         <v>224</v>
@@ -3240,7 +3240,7 @@
         <v>233</v>
       </c>
       <c r="C129" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D129" t="s">
         <v>224</v>
@@ -3254,7 +3254,7 @@
         <v>223</v>
       </c>
       <c r="C130" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D130" t="s">
         <v>224</v>
@@ -3268,7 +3268,7 @@
         <v>225</v>
       </c>
       <c r="C131" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D131" t="s">
         <v>224</v>
@@ -3282,7 +3282,7 @@
         <v>229</v>
       </c>
       <c r="C132" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D132" t="s">
         <v>224</v>
@@ -3296,7 +3296,7 @@
         <v>232</v>
       </c>
       <c r="C133" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D133" t="s">
         <v>224</v>
@@ -3310,7 +3310,7 @@
         <v>226</v>
       </c>
       <c r="C134" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D134" t="s">
         <v>224</v>
@@ -3324,7 +3324,7 @@
         <v>228</v>
       </c>
       <c r="C135" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D135" t="s">
         <v>224</v>
@@ -3338,7 +3338,7 @@
         <v>227</v>
       </c>
       <c r="C136" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D136" t="s">
         <v>224</v>
@@ -3352,7 +3352,7 @@
         <v>240</v>
       </c>
       <c r="C137" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D137" t="s">
         <v>224</v>
@@ -3366,7 +3366,7 @@
         <v>230</v>
       </c>
       <c r="C138" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D138" t="s">
         <v>224</v>
@@ -3380,7 +3380,7 @@
         <v>239</v>
       </c>
       <c r="C139" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D139" t="s">
         <v>224</v>
@@ -3394,7 +3394,7 @@
         <v>243</v>
       </c>
       <c r="C140" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D140" t="s">
         <v>224</v>
@@ -3408,7 +3408,7 @@
         <v>234</v>
       </c>
       <c r="C141" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D141" t="s">
         <v>224</v>
@@ -3422,7 +3422,7 @@
         <v>238</v>
       </c>
       <c r="C142" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D142" t="s">
         <v>224</v>
@@ -3436,7 +3436,7 @@
         <v>237</v>
       </c>
       <c r="C143" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D143" t="s">
         <v>224</v>
@@ -3450,7 +3450,7 @@
         <v>241</v>
       </c>
       <c r="C144" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D144" t="s">
         <v>224</v>
@@ -3464,7 +3464,7 @@
         <v>235</v>
       </c>
       <c r="C145" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D145" t="s">
         <v>224</v>
@@ -3478,7 +3478,7 @@
         <v>160</v>
       </c>
       <c r="C146" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D146" t="s">
         <v>161</v>
@@ -3492,7 +3492,7 @@
         <v>168</v>
       </c>
       <c r="C147" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D147" t="s">
         <v>161</v>
@@ -3506,7 +3506,7 @@
         <v>187</v>
       </c>
       <c r="C148" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D148" t="s">
         <v>161</v>
@@ -3520,7 +3520,7 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D149" t="s">
         <v>120</v>
@@ -3534,7 +3534,7 @@
         <v>118</v>
       </c>
       <c r="C150" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D150" t="s">
         <v>119</v>
@@ -3548,7 +3548,7 @@
         <v>156</v>
       </c>
       <c r="C151" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D151" t="s">
         <v>120</v>
@@ -3562,7 +3562,7 @@
         <v>162</v>
       </c>
       <c r="C152" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D152" t="s">
         <v>161</v>
@@ -3576,7 +3576,7 @@
         <v>181</v>
       </c>
       <c r="C153" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D153" t="s">
         <v>161</v>
@@ -3590,7 +3590,7 @@
         <v>184</v>
       </c>
       <c r="C154" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D154" t="s">
         <v>161</v>
@@ -3604,7 +3604,7 @@
         <v>166</v>
       </c>
       <c r="C155" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D155" t="s">
         <v>161</v>
@@ -3618,7 +3618,7 @@
         <v>170</v>
       </c>
       <c r="C156" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D156" t="s">
         <v>161</v>
@@ -3632,7 +3632,7 @@
         <v>171</v>
       </c>
       <c r="C157" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D157" t="s">
         <v>161</v>
@@ -3646,7 +3646,7 @@
         <v>175</v>
       </c>
       <c r="C158" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D158" t="s">
         <v>161</v>
@@ -3660,7 +3660,7 @@
         <v>177</v>
       </c>
       <c r="C159" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D159" t="s">
         <v>161</v>
@@ -3674,7 +3674,7 @@
         <v>165</v>
       </c>
       <c r="C160" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D160" t="s">
         <v>161</v>
@@ -3688,7 +3688,7 @@
         <v>167</v>
       </c>
       <c r="C161" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D161" t="s">
         <v>161</v>
@@ -3702,7 +3702,7 @@
         <v>180</v>
       </c>
       <c r="C162" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D162" t="s">
         <v>161</v>
@@ -3716,7 +3716,7 @@
         <v>164</v>
       </c>
       <c r="C163" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D163" t="s">
         <v>161</v>
@@ -3730,7 +3730,7 @@
         <v>158</v>
       </c>
       <c r="C164" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D164" t="s">
         <v>161</v>
@@ -3744,7 +3744,7 @@
         <v>174</v>
       </c>
       <c r="C165" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D165" t="s">
         <v>161</v>
@@ -3758,7 +3758,7 @@
         <v>159</v>
       </c>
       <c r="C166" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D166" t="s">
         <v>161</v>
@@ -3772,7 +3772,7 @@
         <v>182</v>
       </c>
       <c r="C167" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D167" t="s">
         <v>161</v>
@@ -3786,7 +3786,7 @@
         <v>290</v>
       </c>
       <c r="C168" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D168" t="s">
         <v>46</v>
@@ -3800,7 +3800,7 @@
         <v>291</v>
       </c>
       <c r="C169" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D169" t="s">
         <v>46</v>
@@ -3814,7 +3814,7 @@
         <v>283</v>
       </c>
       <c r="C170" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D170" t="s">
         <v>46</v>
@@ -3828,7 +3828,7 @@
         <v>293</v>
       </c>
       <c r="C171" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D171" t="s">
         <v>46</v>
@@ -3842,7 +3842,7 @@
         <v>151</v>
       </c>
       <c r="C172" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D172" t="s">
         <v>120</v>
@@ -3856,7 +3856,7 @@
         <v>157</v>
       </c>
       <c r="C173" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D173" t="s">
         <v>120</v>
@@ -3870,7 +3870,7 @@
         <v>69</v>
       </c>
       <c r="C174" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D174" t="s">
         <v>64</v>
@@ -3884,7 +3884,7 @@
         <v>70</v>
       </c>
       <c r="C175" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D175" t="s">
         <v>64</v>
@@ -3898,7 +3898,7 @@
         <v>72</v>
       </c>
       <c r="C176" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D176" t="s">
         <v>64</v>
@@ -3912,7 +3912,7 @@
         <v>216</v>
       </c>
       <c r="C177" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D177" t="s">
         <v>217</v>
@@ -3926,7 +3926,7 @@
         <v>218</v>
       </c>
       <c r="C178" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D178" t="s">
         <v>217</v>
@@ -3940,7 +3940,7 @@
         <v>219</v>
       </c>
       <c r="C179" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D179" t="s">
         <v>217</v>
@@ -3954,7 +3954,7 @@
         <v>220</v>
       </c>
       <c r="C180" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D180" t="s">
         <v>217</v>
@@ -3968,7 +3968,7 @@
         <v>221</v>
       </c>
       <c r="C181" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D181" t="s">
         <v>217</v>
@@ -3982,7 +3982,7 @@
         <v>222</v>
       </c>
       <c r="C182" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D182" t="s">
         <v>217</v>
@@ -3996,7 +3996,7 @@
         <v>149</v>
       </c>
       <c r="C183" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D183" t="s">
         <v>120</v>
@@ -4010,7 +4010,7 @@
         <v>150</v>
       </c>
       <c r="C184" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D184" t="s">
         <v>120</v>
@@ -4024,7 +4024,7 @@
         <v>152</v>
       </c>
       <c r="C185" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D185" t="s">
         <v>120</v>
@@ -4038,7 +4038,7 @@
         <v>154</v>
       </c>
       <c r="C186" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D186" t="s">
         <v>120</v>
@@ -4052,7 +4052,7 @@
         <v>155</v>
       </c>
       <c r="C187" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D187" t="s">
         <v>120</v>
@@ -4066,7 +4066,7 @@
         <v>81</v>
       </c>
       <c r="C188" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D188" t="s">
         <v>64</v>
@@ -4080,7 +4080,7 @@
         <v>89</v>
       </c>
       <c r="C189" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D189" t="s">
         <v>64</v>
@@ -4094,7 +4094,7 @@
         <v>82</v>
       </c>
       <c r="C190" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D190" t="s">
         <v>64</v>
@@ -4108,7 +4108,7 @@
         <v>84</v>
       </c>
       <c r="C191" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D191" t="s">
         <v>64</v>
@@ -4122,7 +4122,7 @@
         <v>262</v>
       </c>
       <c r="C192" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D192" t="s">
         <v>263</v>
@@ -4136,7 +4136,7 @@
         <v>264</v>
       </c>
       <c r="C193" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D193" t="s">
         <v>263</v>
@@ -4150,7 +4150,7 @@
         <v>265</v>
       </c>
       <c r="C194" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D194" t="s">
         <v>263</v>
@@ -4164,7 +4164,7 @@
         <v>266</v>
       </c>
       <c r="C195" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D195" t="s">
         <v>263</v>
@@ -4178,7 +4178,7 @@
         <v>267</v>
       </c>
       <c r="C196" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D196" t="s">
         <v>263</v>
@@ -4192,7 +4192,7 @@
         <v>276</v>
       </c>
       <c r="C197" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D197" t="s">
         <v>306</v>
@@ -4206,7 +4206,7 @@
         <v>277</v>
       </c>
       <c r="C198" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D198" t="s">
         <v>306</v>
@@ -4220,7 +4220,7 @@
         <v>278</v>
       </c>
       <c r="C199" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D199" t="s">
         <v>306</v>
@@ -4234,7 +4234,7 @@
         <v>100</v>
       </c>
       <c r="C200" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D200" t="s">
         <v>64</v>
@@ -4248,7 +4248,7 @@
         <v>94</v>
       </c>
       <c r="C201" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D201" t="s">
         <v>64</v>
@@ -4262,7 +4262,7 @@
         <v>95</v>
       </c>
       <c r="C202" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D202" t="s">
         <v>64</v>
@@ -4276,7 +4276,7 @@
         <v>101</v>
       </c>
       <c r="C203" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D203" t="s">
         <v>64</v>
@@ -4290,7 +4290,7 @@
         <v>295</v>
       </c>
       <c r="C204" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D204" t="s">
         <v>46</v>
@@ -4304,7 +4304,7 @@
         <v>296</v>
       </c>
       <c r="C205" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D205" t="s">
         <v>46</v>
@@ -4318,7 +4318,7 @@
         <v>297</v>
       </c>
       <c r="C206" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D206" t="s">
         <v>46</v>
@@ -4332,7 +4332,7 @@
         <v>298</v>
       </c>
       <c r="C207" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D207" t="s">
         <v>46</v>
@@ -4346,7 +4346,7 @@
         <v>299</v>
       </c>
       <c r="C208" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D208" t="s">
         <v>46</v>
@@ -4360,7 +4360,7 @@
         <v>56</v>
       </c>
       <c r="C209" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D209" t="s">
         <v>45</v>
@@ -4374,7 +4374,7 @@
         <v>54</v>
       </c>
       <c r="C210" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D210" t="s">
         <v>45</v>
@@ -4388,7 +4388,7 @@
         <v>257</v>
       </c>
       <c r="C211" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D211" t="s">
         <v>245</v>
@@ -4402,7 +4402,7 @@
         <v>258</v>
       </c>
       <c r="C212" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D212" t="s">
         <v>245</v>
@@ -4416,7 +4416,7 @@
         <v>249</v>
       </c>
       <c r="C213" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D213" t="s">
         <v>245</v>
@@ -4430,7 +4430,7 @@
         <v>255</v>
       </c>
       <c r="C214" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D214" t="s">
         <v>245</v>
@@ -4444,7 +4444,7 @@
         <v>246</v>
       </c>
       <c r="C215" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D215" t="s">
         <v>245</v>
@@ -4458,7 +4458,7 @@
         <v>248</v>
       </c>
       <c r="C216" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D216" t="s">
         <v>245</v>
@@ -4472,7 +4472,7 @@
         <v>250</v>
       </c>
       <c r="C217" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D217" t="s">
         <v>245</v>
@@ -4486,7 +4486,7 @@
         <v>247</v>
       </c>
       <c r="C218" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D218" t="s">
         <v>245</v>
@@ -4500,7 +4500,7 @@
         <v>253</v>
       </c>
       <c r="C219" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D219" t="s">
         <v>245</v>
@@ -4514,7 +4514,7 @@
         <v>251</v>
       </c>
       <c r="C220" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D220" t="s">
         <v>245</v>
@@ -4528,7 +4528,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D221" t="s">
         <v>245</v>
@@ -4542,7 +4542,7 @@
         <v>260</v>
       </c>
       <c r="C222" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D222" t="s">
         <v>245</v>
@@ -4556,7 +4556,7 @@
         <v>39</v>
       </c>
       <c r="C223" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D223" t="s">
         <v>34</v>
@@ -4570,7 +4570,7 @@
         <v>40</v>
       </c>
       <c r="C224" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D224" t="s">
         <v>34</v>
@@ -4584,7 +4584,7 @@
         <v>37</v>
       </c>
       <c r="C225" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D225" t="s">
         <v>34</v>
@@ -4598,7 +4598,7 @@
         <v>41</v>
       </c>
       <c r="C226" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D226" t="s">
         <v>34</v>
@@ -4612,7 +4612,7 @@
         <v>33</v>
       </c>
       <c r="C227" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D227" t="s">
         <v>34</v>
@@ -4626,7 +4626,7 @@
         <v>35</v>
       </c>
       <c r="C228" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D228" t="s">
         <v>34</v>
@@ -4640,7 +4640,7 @@
         <v>36</v>
       </c>
       <c r="C229" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D229" t="s">
         <v>34</v>
@@ -4654,7 +4654,7 @@
         <v>38</v>
       </c>
       <c r="C230" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D230" t="s">
         <v>34</v>
@@ -4668,7 +4668,7 @@
         <v>108</v>
       </c>
       <c r="C231" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D231" t="s">
         <v>105</v>
@@ -4682,7 +4682,7 @@
         <v>109</v>
       </c>
       <c r="C232" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D232" t="s">
         <v>105</v>
@@ -4696,7 +4696,7 @@
         <v>111</v>
       </c>
       <c r="C233" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D233" t="s">
         <v>105</v>
@@ -4710,7 +4710,7 @@
         <v>112</v>
       </c>
       <c r="C234" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D234" t="s">
         <v>105</v>
@@ -4724,7 +4724,7 @@
         <v>116</v>
       </c>
       <c r="C235" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D235" t="s">
         <v>105</v>
@@ -4738,7 +4738,7 @@
         <v>6</v>
       </c>
       <c r="C236" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D236" t="s">
         <v>1</v>
@@ -4752,7 +4752,7 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D237" t="s">
         <v>1</v>
@@ -4766,7 +4766,7 @@
         <v>10</v>
       </c>
       <c r="C238" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D238" t="s">
         <v>1</v>
@@ -4780,7 +4780,7 @@
         <v>9</v>
       </c>
       <c r="C239" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D239" t="s">
         <v>1</v>
@@ -4794,7 +4794,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D240" t="s">
         <v>1</v>
@@ -4808,7 +4808,7 @@
         <v>17</v>
       </c>
       <c r="C241" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D241" t="s">
         <v>1</v>
@@ -4822,7 +4822,7 @@
         <v>4</v>
       </c>
       <c r="C242" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D242" t="s">
         <v>1</v>
@@ -4836,7 +4836,7 @@
         <v>5</v>
       </c>
       <c r="C243" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D243" t="s">
         <v>1</v>
@@ -4850,7 +4850,7 @@
         <v>14</v>
       </c>
       <c r="C244" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D244" t="s">
         <v>1</v>
@@ -4864,7 +4864,7 @@
         <v>18</v>
       </c>
       <c r="C245" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D245" t="s">
         <v>1</v>
@@ -4878,7 +4878,7 @@
         <v>2</v>
       </c>
       <c r="C246" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D246" t="s">
         <v>1</v>
@@ -4892,7 +4892,7 @@
         <v>26</v>
       </c>
       <c r="C247" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D247" t="s">
         <v>1</v>
@@ -4906,7 +4906,7 @@
         <v>28</v>
       </c>
       <c r="C248" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D248" t="s">
         <v>1</v>
@@ -4920,7 +4920,7 @@
         <v>13</v>
       </c>
       <c r="C249" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D249" t="s">
         <v>1</v>
@@ -4934,7 +4934,7 @@
         <v>44</v>
       </c>
       <c r="C250" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D250" t="s">
         <v>45</v>
@@ -4948,7 +4948,7 @@
         <v>47</v>
       </c>
       <c r="C251" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D251" t="s">
         <v>45</v>
@@ -4962,7 +4962,7 @@
         <v>49</v>
       </c>
       <c r="C252" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D252" t="s">
         <v>45</v>
@@ -4976,7 +4976,7 @@
         <v>50</v>
       </c>
       <c r="C253" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D253" t="s">
         <v>45</v>
@@ -4990,7 +4990,7 @@
         <v>62</v>
       </c>
       <c r="C254" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D254" t="s">
         <v>45</v>
@@ -5004,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D255" t="s">
         <v>1</v>
@@ -5018,7 +5018,7 @@
         <v>3</v>
       </c>
       <c r="C256" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D256" t="s">
         <v>1</v>
@@ -5032,7 +5032,7 @@
         <v>11</v>
       </c>
       <c r="C257" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D257" t="s">
         <v>1</v>
@@ -5046,7 +5046,7 @@
         <v>12</v>
       </c>
       <c r="C258" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D258" t="s">
         <v>1</v>
@@ -5060,7 +5060,7 @@
         <v>24</v>
       </c>
       <c r="C259" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D259" t="s">
         <v>1</v>
@@ -5074,7 +5074,7 @@
         <v>21</v>
       </c>
       <c r="C260" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D260" t="s">
         <v>1</v>
@@ -5088,7 +5088,7 @@
         <v>25</v>
       </c>
       <c r="C261" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D261" t="s">
         <v>1</v>
@@ -5102,7 +5102,7 @@
         <v>20</v>
       </c>
       <c r="C262" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D262" t="s">
         <v>1</v>
@@ -5116,7 +5116,7 @@
         <v>22</v>
       </c>
       <c r="C263" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D263" t="s">
         <v>1</v>
@@ -5130,7 +5130,7 @@
         <v>23</v>
       </c>
       <c r="C264" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D264" t="s">
         <v>1</v>
@@ -5144,7 +5144,7 @@
         <v>31</v>
       </c>
       <c r="C265" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D265" t="s">
         <v>32</v>
@@ -5158,7 +5158,7 @@
         <v>92</v>
       </c>
       <c r="C266" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D266" t="s">
         <v>64</v>
@@ -5172,7 +5172,7 @@
         <v>58</v>
       </c>
       <c r="C267" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D267" t="s">
         <v>45</v>
@@ -5186,7 +5186,7 @@
         <v>29</v>
       </c>
       <c r="C268" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D268" t="s">
         <v>30</v>
@@ -5200,7 +5200,7 @@
         <v>289</v>
       </c>
       <c r="C269" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D269" t="s">
         <v>46</v>
@@ -5214,7 +5214,7 @@
         <v>281</v>
       </c>
       <c r="C270" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D270" t="s">
         <v>46</v>
@@ -5228,7 +5228,7 @@
         <v>59</v>
       </c>
       <c r="C271" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D271" t="s">
         <v>45</v>
@@ -5242,7 +5242,7 @@
         <v>256</v>
       </c>
       <c r="C272" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D272" t="s">
         <v>245</v>
@@ -5256,7 +5256,7 @@
         <v>42</v>
       </c>
       <c r="C273" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D273" t="s">
         <v>305</v>
@@ -5270,7 +5270,7 @@
         <v>79</v>
       </c>
       <c r="C274" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D274" t="s">
         <v>64</v>
@@ -5284,7 +5284,7 @@
         <v>173</v>
       </c>
       <c r="C275" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D275" t="s">
         <v>161</v>
@@ -5298,7 +5298,7 @@
         <v>51</v>
       </c>
       <c r="C276" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D276" t="s">
         <v>45</v>
@@ -5312,7 +5312,7 @@
         <v>288</v>
       </c>
       <c r="C277" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D277" t="s">
         <v>46</v>
@@ -5326,7 +5326,7 @@
         <v>48</v>
       </c>
       <c r="C278" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D278" t="s">
         <v>45</v>
@@ -5340,7 +5340,7 @@
         <v>60</v>
       </c>
       <c r="C279" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D279" t="s">
         <v>45</v>
@@ -5354,7 +5354,7 @@
         <v>110</v>
       </c>
       <c r="C280" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D280" t="s">
         <v>105</v>
@@ -5368,7 +5368,7 @@
         <v>214</v>
       </c>
       <c r="C281" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D281" t="s">
         <v>215</v>
@@ -5382,7 +5382,7 @@
         <v>292</v>
       </c>
       <c r="C282" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D282" t="s">
         <v>46</v>
@@ -5396,7 +5396,7 @@
         <v>61</v>
       </c>
       <c r="C283" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D283" t="s">
         <v>45</v>
@@ -5410,7 +5410,7 @@
         <v>102</v>
       </c>
       <c r="C284" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D284" t="s">
         <v>103</v>
@@ -5424,7 +5424,7 @@
         <v>115</v>
       </c>
       <c r="C285" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D285" t="s">
         <v>105</v>
@@ -5438,7 +5438,7 @@
         <v>242</v>
       </c>
       <c r="C286" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D286" t="s">
         <v>224</v>
@@ -5449,13 +5449,13 @@
         <v>99999</v>
       </c>
       <c r="B287" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C287" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D287" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -5463,13 +5463,13 @@
         <v>99993</v>
       </c>
       <c r="B288" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C288" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D288" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -5477,13 +5477,13 @@
         <v>99992</v>
       </c>
       <c r="B289" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C289" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D289" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
@@ -5491,13 +5491,13 @@
         <v>99991</v>
       </c>
       <c r="B290" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C290" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D290" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -5507,15 +5507,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <mad72c545b54457b81618ddb1b162d54 xmlns="02c4650c-f8e4-4645-b522-cf5020ef161b">
@@ -5549,7 +5540,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="VEKA-beleidswerk" ma:contentTypeID="0x0101006F9C7C1746960341B67A546B27CC8B9802000CA6108F60948243A95B6C35464CAA30" ma:contentTypeVersion="11" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="3e9a0a566ef87c4db10ef35b6ca8a7f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="02c4650c-f8e4-4645-b522-cf5020ef161b" xmlns:ns3="589c7f2b-8d26-4a4a-ad96-e0afba0f4786" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="62060e7f2857e9fcd70439c0429ff9c2" ns2:_="" ns3:_="">
     <xsd:import namespace="02c4650c-f8e4-4645-b522-cf5020ef161b"/>
@@ -5807,11 +5798,11 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -5861,15 +5852,16 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05CECBC0-79AB-4DFC-9DE2-5CD49878AB1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3081CEAD-5D3F-4EC3-A32B-594192605948}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="589c7f2b-8d26-4a4a-ad96-e0afba0f4786"/>
@@ -5886,7 +5878,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B287EE5-D5C2-412C-BAF2-22A8A10C4793}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5905,7 +5897,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84B8E422-E983-43D7-8F15-9DA5E49C71E6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
@@ -5913,10 +5905,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{170F1128-0224-4D39-A9D4-212B25CE7E80}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05CECBC0-79AB-4DFC-9DE2-5CD49878AB1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
